--- a/references/markdown_tables.xlsx
+++ b/references/markdown_tables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\000 - Arquivos\Educação\Habilidades e Treinamentos\Ciência de Dados\Projetos Finais\ds_projeto_final_5_modelo_clusterizacao_classificacao_app_delivery\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9594F321-1484-4C87-9370-CEAF89A29F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8579119-FC21-4D38-A5B0-49A840CEB26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{7292E81B-BEA0-441A-B0C0-C80AAE2EAF96}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="261">
   <si>
     <t>Evidente</t>
   </si>
@@ -771,14 +771,77 @@
     <t>O objetivo é que o modelo preveja o comportamento dos consumidores e torne possível aplicá-lo a toda a base de clientes, permitindo que a empresa identifique os clientes que têm maior probabilidade de aceitar a campanha, **otimizando assim os resultados das campanhas e tornando-as altamente lucrativas**</t>
   </si>
   <si>
-    <t>ROC-AUC</t>
+    <t>ROC AUC</t>
+  </si>
+  <si>
+    <t>1º</t>
+  </si>
+  <si>
+    <t>2º</t>
+  </si>
+  <si>
+    <t>3º</t>
+  </si>
+  <si>
+    <t>4º</t>
+  </si>
+  <si>
+    <t>5º</t>
+  </si>
+  <si>
+    <t>6º</t>
+  </si>
+  <si>
+    <t>7º</t>
+  </si>
+  <si>
+    <t>8º</t>
+  </si>
+  <si>
+    <t>9º</t>
+  </si>
+  <si>
+    <t>10º</t>
+  </si>
+  <si>
+    <t>11º</t>
+  </si>
+  <si>
+    <t>SVC</t>
+  </si>
+  <si>
+    <t>ExtraTreesClassifier</t>
+  </si>
+  <si>
+    <t>RandomForestClassifier</t>
+  </si>
+  <si>
+    <t>GradientBoostingClassifier</t>
+  </si>
+  <si>
+    <t>AdaBoostClassifier</t>
+  </si>
+  <si>
+    <t>XGBClassifier</t>
+  </si>
+  <si>
+    <t>MLPClassifier</t>
+  </si>
+  <si>
+    <t>Rede Neural</t>
+  </si>
+  <si>
+    <t>Ensemble</t>
+  </si>
+  <si>
+    <t>Tradicional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -796,6 +859,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -821,7 +892,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -829,19 +900,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -857,6 +940,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1196,72 +1291,72 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="129.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="27.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="129.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2293,14 +2388,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="8"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2609,153 +2704,384 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025C8251-4A88-410D-AE97-D5E094F5545E}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
-    <col min="2" max="7" width="20" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
+    <col min="2" max="7" width="22.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="2"/>
+    <col min="9" max="9" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="G4" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="I4" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="I5" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="D7" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E11" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F11" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="G11" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C13" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D13" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E13" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F13" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>117</v>
+      <c r="G13" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
